--- a/output/laminas_comunales/comunal_i_ingr_a_2024_aysen.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2024_aysen.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>6.227546270716089</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>21.68573681780652</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>4.855691795914674</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>4.459967466313075</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>11.79354330105535</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>11.4107986250308</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -537,9 +514,6 @@
       <c r="E8">
         <v>6.406141236504292</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -559,9 +533,6 @@
       <c r="E9">
         <v>5.400941124297676</v>
       </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -581,9 +552,6 @@
       <c r="E10">
         <v>7.183827394104814</v>
       </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -602,9 +570,6 @@
       </c>
       <c r="E11">
         <v>12.69164554167375</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_a_2024_aysen.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2024_aysen.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -404,7 +404,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="B3">
@@ -423,152 +423,171 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cisnes</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B4">
-        <v>1203306.88</v>
+        <v>1240594</v>
       </c>
       <c r="C4">
-        <v>1147583.75</v>
+        <v>1166918.62</v>
       </c>
       <c r="D4">
-        <v>55723.12999999989</v>
+        <v>73675.37999999989</v>
       </c>
       <c r="E4">
-        <v>4.855691795914674</v>
+        <v>6.313669071455896</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cochrane</t>
+          <t>Cisnes</t>
         </is>
       </c>
       <c r="B5">
-        <v>1203263</v>
+        <v>1203306.88</v>
       </c>
       <c r="C5">
-        <v>1151889.12</v>
+        <v>1147583.75</v>
       </c>
       <c r="D5">
-        <v>51373.87999999989</v>
+        <v>55723.12999999989</v>
       </c>
       <c r="E5">
-        <v>4.459967466313075</v>
+        <v>4.855691795914674</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Río Ibáñez</t>
+          <t>Cochrane</t>
         </is>
       </c>
       <c r="B6">
-        <v>1187455.5</v>
+        <v>1203263</v>
       </c>
       <c r="C6">
-        <v>1062186.12</v>
+        <v>1151889.12</v>
       </c>
       <c r="D6">
-        <v>125269.3799999999</v>
+        <v>51373.87999999989</v>
       </c>
       <c r="E6">
-        <v>11.79354330105535</v>
+        <v>4.459967466313075</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chile Chico</t>
+          <t>Río Ibáñez</t>
         </is>
       </c>
       <c r="B7">
-        <v>1179036.25</v>
+        <v>1187455.5</v>
       </c>
       <c r="C7">
-        <v>1058278.25</v>
+        <v>1062186.12</v>
       </c>
       <c r="D7">
-        <v>120758</v>
+        <v>125269.3799999999</v>
       </c>
       <c r="E7">
-        <v>11.4107986250308</v>
+        <v>11.79354330105535</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tortel</t>
+          <t>Chile Chico</t>
         </is>
       </c>
       <c r="B8">
-        <v>1171820.38</v>
+        <v>1179036.25</v>
       </c>
       <c r="C8">
-        <v>1101271.38</v>
+        <v>1058278.25</v>
       </c>
       <c r="D8">
-        <v>70549</v>
+        <v>120758</v>
       </c>
       <c r="E8">
-        <v>6.406141236504292</v>
+        <v>11.4107986250308</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Tortel</t>
         </is>
       </c>
       <c r="B9">
-        <v>1171634.88</v>
+        <v>1171820.38</v>
       </c>
       <c r="C9">
-        <v>1111598.12</v>
+        <v>1101271.38</v>
       </c>
       <c r="D9">
-        <v>60036.75999999978</v>
+        <v>70549</v>
       </c>
       <c r="E9">
-        <v>5.400941124297676</v>
+        <v>6.406141236504292</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Guaitecas</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="B10">
-        <v>1124659</v>
+        <v>1171634.88</v>
       </c>
       <c r="C10">
-        <v>1049280.5</v>
+        <v>1111598.12</v>
       </c>
       <c r="D10">
-        <v>75378.5</v>
+        <v>60036.75999999978</v>
       </c>
       <c r="E10">
-        <v>7.183827394104814</v>
+        <v>5.400941124297676</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>1124659</v>
+      </c>
+      <c r="C11">
+        <v>1049280.5</v>
+      </c>
+      <c r="D11">
+        <v>75378.5</v>
+      </c>
+      <c r="E11">
+        <v>7.183827394104814</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Lago Verde</t>
         </is>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>1071904.62</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <v>951183.75</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>120720.8700000001</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <v>12.69164554167375</v>
       </c>
     </row>
@@ -667,7 +686,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="B9">

--- a/output/laminas_comunales/comunal_i_ingr_a_2024_aysen.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2024_aysen.xlsx
@@ -598,7 +598,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -607,20 +607,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aysén</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>1171634.88</v>
+          <t>Río Ibáñez</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -629,88 +621,61 @@
           <t>Chile Chico</t>
         </is>
       </c>
-      <c r="B3">
-        <v>1179036.25</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cisnes</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>1203306.88</v>
+          <t>Lago Verde</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cochrane</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>1203263</v>
+          <t>Coyhaique</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coyhaique</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>1285710.5</v>
+          <t>Cisnes</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Guaitecas</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>1124659</v>
+          <t>Tortel</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lago Verde</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>1071904.62</v>
+          <t>O'Higgins</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>1242065.25</v>
+          <t>Cochrane</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Río Ibáñez</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>1187455.5</v>
+          <t>Guaitecas</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tortel</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>1171820.38</v>
+          <t>Aysén</t>
+        </is>
       </c>
     </row>
   </sheetData>
